--- a/tools/importer/reports/import-nsman-article.report.xlsx
+++ b/tools/importer/reports/import-nsman-article.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
   <si>
     <t>_reportFile</t>
   </si>
@@ -58,6 +58,27 @@
     <t>https://www.safra.sg/nsman-magazine</t>
   </si>
   <si>
+    <t>nsman-magazine/fun-activities/fun-activities/2026/10/23/pov-clayface-film-review.report.json</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>nsman-magazine/fun-activities/fun-activities/2026/10/23/pov-clayface-film-review</t>
+  </si>
+  <si>
+    <t>nsman-article</t>
+  </si>
+  <si>
+    <t>2026-10-27T05:19:42.159Z</t>
+  </si>
+  <si>
+    <t>POV: DC goes full body horror, and I had a bloody good time with it | SAFRA</t>
+  </si>
+  <si>
+    <t>https://www.safra.sg/nsman-magazine/fun-activities/Fun-activities/2026/10/23/pov-Clayface-film-review</t>
+  </si>
+  <si>
     <t>nsman-magazine/spotlight/editor-picks/2026/10/26/every-lap-counts-safra-swim-for-hope-2026.report.json</t>
   </si>
   <si>
@@ -65,9 +86,6 @@
   </si>
   <si>
     <t>nsman-magazine/spotlight/editor-picks/2026/10/26/every-lap-counts-safra-swim-for-hope-2026</t>
-  </si>
-  <si>
-    <t>nsman-article</t>
   </si>
   <si>
     <t>2026-10-27T03:33:07.891Z</t>
@@ -465,7 +483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -554,6 +572,32 @@
         <v>21</v>
       </c>
     </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tools/importer/reports/import-nsman-article.report.xlsx
+++ b/tools/importer/reports/import-nsman-article.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
   <si>
     <t>_reportFile</t>
   </si>
@@ -77,6 +77,21 @@
   </si>
   <si>
     <t>https://www.safra.sg/nsman-magazine/fun-activities/Fun-activities/2026/10/23/pov-Clayface-film-review</t>
+  </si>
+  <si>
+    <t>nsman-magazine/parenting/parenting/2026/10/21/press-play-on-purposeful-screen-time.report.json</t>
+  </si>
+  <si>
+    <t>nsman-magazine/parenting/parenting/2026/10/21/press-play-on-purposeful-screen-time</t>
+  </si>
+  <si>
+    <t>2026-10-27T05:42:49.143Z</t>
+  </si>
+  <si>
+    <t>Press Play On Purposeful Screen Time | SAFRA</t>
+  </si>
+  <si>
+    <t>https://www.safra.sg/nsman-magazine/parenting/parenting/2026/10/21/press-play-on-purposeful-screen-time</t>
   </si>
   <si>
     <t>nsman-magazine/spotlight/editor-picks/2026/10/26/every-lap-counts-safra-swim-for-hope-2026.report.json</t>
@@ -483,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -577,10 +592,10 @@
         <v>22</v>
       </c>
       <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
         <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -589,13 +604,39 @@
         <v>18</v>
       </c>
       <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
         <v>25</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>26</v>
       </c>
-      <c r="H4" t="s">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-nsman-article.report.xlsx
+++ b/tools/importer/reports/import-nsman-article.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
   <si>
     <t>_reportFile</t>
   </si>
@@ -58,16 +58,31 @@
     <t>https://www.safra.sg/nsman-magazine</t>
   </si>
   <si>
+    <t>nsman-magazine/eat-and-drink/eat-and-drink/2026/10/20/eat-your-way-around-singapore.report.json</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>nsman-magazine/eat-and-drink/eat-and-drink/2026/10/20/eat-your-way-around-singapore</t>
+  </si>
+  <si>
+    <t>nsman-article</t>
+  </si>
+  <si>
+    <t>2026-10-27T06:04:06.877Z</t>
+  </si>
+  <si>
+    <t>Eat Your Way Around Singapore: The New Dining Spots and Makan Deals Worth Your Time And Money | SAFRA</t>
+  </si>
+  <si>
+    <t>https://www.safra.sg/nsman-magazine/eat-and-drink/Eat-and-drink/2026/10/20/eat-your-way-around-Singapore</t>
+  </si>
+  <si>
     <t>nsman-magazine/fun-activities/fun-activities/2026/10/23/pov-clayface-film-review.report.json</t>
   </si>
   <si>
-    <t>[]</t>
-  </si>
-  <si>
     <t>nsman-magazine/fun-activities/fun-activities/2026/10/23/pov-clayface-film-review</t>
-  </si>
-  <si>
-    <t>nsman-article</t>
   </si>
   <si>
     <t>2026-10-27T05:19:42.159Z</t>
@@ -498,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -618,10 +633,10 @@
         <v>27</v>
       </c>
       <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
         <v>28</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -630,13 +645,39 @@
         <v>18</v>
       </c>
       <c r="F5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" t="s">
         <v>30</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>31</v>
       </c>
-      <c r="H5" t="s">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
